--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -256,6 +256,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
   <sheetData/>
 </worksheet>
 </file>
--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -77,7 +77,6 @@
       <c r="B2">
         <v>0.99</v>
       </c>
-      <c r="C2"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Products" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Empty Sheet" sheetId="3" r:id="rId3"/>
+    <sheet name="Types" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -39,9 +40,10 @@
   <borders count="1">
     <border/>
   </borders>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
+    <xf numFmtId="165" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" applyFont="1"/>
   </cellXfs>
 </styleSheet>
@@ -64,8 +66,8 @@
       <c r="B1">
         <v>1.99</v>
       </c>
-      <c r="C1" t="b">
-        <v>0</v>
+      <c r="C1">
+        <v>10</v>
       </c>
     </row>
     <row r="2">
@@ -77,6 +79,9 @@
       <c r="B2">
         <v>0.99</v>
       </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -87,21 +92,21 @@
       <c r="B3">
         <v>2.49</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sum of all fruits</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="B4">
         <f>SUM(B1:B3)</f>
       </c>
-      <c r="C4" s="1">
-        <v>43102.642245</v>
+      <c r="C4" s="3">
+        <f>SUM(C1:C3)</f>
       </c>
     </row>
   </sheetData>
@@ -255,10 +260,107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B10"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Empty string</t>
+        </is>
+      </c>
+      <c r="B4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Empty object</t>
+        </is>
+      </c>
+      <c r="B5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Object as value</t>
+        </is>
+      </c>
+      <c r="B6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Empty array</t>
+        </is>
+      </c>
+      <c r="B7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Default Date</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>43102.642245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Datetime</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>43102.642245</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B10" s="1">
+        <v>43102.642245</v>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -14,9 +14,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <!-- Date format -->
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
-    <!-- DateTime format -->
   </numFmts>
   <fonts count="2">
     <font>

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -336,7 +336,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>43102.642245</v>
+        <v>43102.573495</v>
       </c>
     </row>
     <row r="9">
@@ -346,7 +346,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>43102.642245</v>
+        <v>43102.573495</v>
       </c>
     </row>
     <row r="10">
@@ -356,7 +356,7 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>43102.642245</v>
+        <v>43102.573495</v>
       </c>
     </row>
   </sheetData>

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -94,16 +94,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B5">
         <f>SUM(B1:B3)</f>
       </c>
-      <c r="C4" s="3">
+      <c r="C5" s="3">
         <f>SUM(C1:C3)</f>
       </c>
     </row>

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -22,9 +22,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,12 +38,18 @@
   <borders count="1">
     <border/>
   </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
   <cellXfs count="4">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
     <xf numFmtId="165" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -22,9 +22,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="1"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,12 +38,18 @@
   <borders count="1">
     <border/>
   </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
   <cellXfs count="4">
-    <xf fontId="0" applyFont="1"/>
-    <xf numFmtId="164" applyNumberFormat="1"/>
-    <xf numFmtId="165" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/test/snap/readme.snap.xlsx
+++ b/test/snap/readme.snap.xlsx
@@ -336,7 +336,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>43102.573495</v>
+        <v>43102.57349538194</v>
       </c>
     </row>
     <row r="9">
@@ -346,7 +346,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>43102.573495</v>
+        <v>25569</v>
       </c>
     </row>
     <row r="10">
@@ -356,7 +356,7 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>43102.573495</v>
+        <v>43102.57349538194</v>
       </c>
     </row>
   </sheetData>
